--- a/output/2023/sector_totals_2023.xlsx
+++ b/output/2023/sector_totals_2023.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1604.649073928743</v>
+        <v>1604.649071475108</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>610.0928791606466</v>
+        <v>601.9183695432722</v>
       </c>
       <c r="E3" t="n">
-        <v>352.6222468608576</v>
+        <v>353.639783443182</v>
       </c>
       <c r="F3" t="n">
-        <v>70.69577479034739</v>
+        <v>71.5094237540319</v>
       </c>
       <c r="G3" t="n">
-        <v>4.094720970484224</v>
+        <v>4.062948484350083</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5939.452686319753</v>
+        <v>5939.452683866119</v>
       </c>
       <c r="C16" t="n">
         <v>545.2810410325812</v>
       </c>
       <c r="D16" t="n">
-        <v>4176.430160763768</v>
+        <v>4168.255651146394</v>
       </c>
       <c r="E16" t="n">
-        <v>6778.413801097759</v>
+        <v>6779.431337680084</v>
       </c>
       <c r="F16" t="n">
-        <v>1561.569662142907</v>
+        <v>1562.383311106591</v>
       </c>
       <c r="G16" t="n">
-        <v>31.53947197606009</v>
+        <v>31.50769948992595</v>
       </c>
     </row>
   </sheetData>

--- a/output/2023/sector_totals_2023.xlsx
+++ b/output/2023/sector_totals_2023.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1604.649071475108</v>
+        <v>1703.275558073358</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>601.9183695432722</v>
+        <v>673.07045149882</v>
       </c>
       <c r="E3" t="n">
-        <v>353.639783443182</v>
+        <v>1926.128095425534</v>
       </c>
       <c r="F3" t="n">
-        <v>71.5094237540319</v>
+        <v>169.8615615042263</v>
       </c>
       <c r="G3" t="n">
-        <v>4.062948484350083</v>
+        <v>75.79993292820414</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5939.452683866119</v>
+        <v>6038.079170464369</v>
       </c>
       <c r="C16" t="n">
         <v>545.2810410325812</v>
       </c>
       <c r="D16" t="n">
-        <v>4168.255651146394</v>
+        <v>4239.407733101942</v>
       </c>
       <c r="E16" t="n">
-        <v>6779.431337680084</v>
+        <v>8351.919649662435</v>
       </c>
       <c r="F16" t="n">
-        <v>1562.383311106591</v>
+        <v>1660.735448856786</v>
       </c>
       <c r="G16" t="n">
-        <v>31.50769948992595</v>
+        <v>103.24468393378</v>
       </c>
     </row>
   </sheetData>

--- a/output/2023/sector_totals_2023.xlsx
+++ b/output/2023/sector_totals_2023.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1703.275558073358</v>
+        <v>1602.102911475161</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>101.1726465981964</v>
       </c>
       <c r="D3" t="n">
         <v>673.07045149882</v>
@@ -507,7 +507,7 @@
         <v>169.8615615042263</v>
       </c>
       <c r="G3" t="n">
-        <v>75.79993292820414</v>
+        <v>75.79993292820413</v>
       </c>
     </row>
     <row r="4">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6038.079170464369</v>
+        <v>5936.906523866171</v>
       </c>
       <c r="C16" t="n">
-        <v>545.2810410325812</v>
+        <v>646.4536876307777</v>
       </c>
       <c r="D16" t="n">
         <v>4239.407733101942</v>

--- a/output/2023/sector_totals_2023.xlsx
+++ b/output/2023/sector_totals_2023.xlsx
@@ -470,7 +470,7 @@
         <v>2595.73</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>313.3413</v>
       </c>
       <c r="D2" t="n">
         <v>1410</v>
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1602.102911475161</v>
+        <v>1733.439382439184</v>
       </c>
       <c r="C3" t="n">
-        <v>101.1726465981964</v>
+        <v>114.9055299929168</v>
       </c>
       <c r="D3" t="n">
-        <v>673.07045149882</v>
+        <v>691.4897039261906</v>
       </c>
       <c r="E3" t="n">
-        <v>1926.128095425534</v>
+        <v>2141.270884832333</v>
       </c>
       <c r="F3" t="n">
-        <v>169.8615615042263</v>
+        <v>183.0528173406445</v>
       </c>
       <c r="G3" t="n">
-        <v>75.79993292820413</v>
+        <v>85.75107534256469</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5936.906523866171</v>
+        <v>6068.242994830194</v>
       </c>
       <c r="C16" t="n">
-        <v>646.4536876307777</v>
+        <v>973.5278710254981</v>
       </c>
       <c r="D16" t="n">
-        <v>4239.407733101942</v>
+        <v>4257.826985529312</v>
       </c>
       <c r="E16" t="n">
-        <v>8351.919649662435</v>
+        <v>8567.062439069236</v>
       </c>
       <c r="F16" t="n">
-        <v>1660.735448856786</v>
+        <v>1673.926704693204</v>
       </c>
       <c r="G16" t="n">
-        <v>103.24468393378</v>
+        <v>113.1958263481406</v>
       </c>
     </row>
   </sheetData>

--- a/output/2023/sector_totals_2023.xlsx
+++ b/output/2023/sector_totals_2023.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1733.439382439184</v>
+        <v>1455.722107292333</v>
       </c>
       <c r="C3" t="n">
-        <v>114.9055299929168</v>
+        <v>103.9850228864146</v>
       </c>
       <c r="D3" t="n">
-        <v>691.4897039261906</v>
+        <v>584.1940258671902</v>
       </c>
       <c r="E3" t="n">
-        <v>2141.270884832333</v>
+        <v>1908.467732705251</v>
       </c>
       <c r="F3" t="n">
-        <v>183.0528173406445</v>
+        <v>157.737357387463</v>
       </c>
       <c r="G3" t="n">
-        <v>85.75107534256469</v>
+        <v>78.00271512360187</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6068.242994830194</v>
+        <v>5790.525719683343</v>
       </c>
       <c r="C16" t="n">
-        <v>973.5278710254981</v>
+        <v>962.6073639189958</v>
       </c>
       <c r="D16" t="n">
-        <v>4257.826985529312</v>
+        <v>4150.531307470312</v>
       </c>
       <c r="E16" t="n">
-        <v>8567.062439069236</v>
+        <v>8334.259286942153</v>
       </c>
       <c r="F16" t="n">
-        <v>1673.926704693204</v>
+        <v>1648.611244740022</v>
       </c>
       <c r="G16" t="n">
-        <v>113.1958263481406</v>
+        <v>105.4474661291777</v>
       </c>
     </row>
   </sheetData>
